--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>212000</v>
+        <v>213000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>363670.4980842912</v>
+        <v>363557.4712643678</v>
       </c>
       <c r="H9" t="n">
-        <v>-12000</v>
+        <v>-30000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.05357142857142857</v>
+        <v>-0.1234567901234568</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -641,21 +641,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1328559.61</v>
+        <v>1328986.66</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dec 2025</t>
+          <t>Jan 2026</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1101106.887024793</v>
+        <v>1104597.812561983</v>
       </c>
       <c r="H6" t="n">
-        <v>31594.05000000005</v>
+        <v>24724.11999999988</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02435997606597977</v>
+        <v>0.01895639814971599</v>
       </c>
     </row>
     <row r="7">
@@ -719,21 +719,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>Feb 2026</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4.581666666666664</v>
+        <v>4.578333333333331</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2999999999999998</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07499999999999996</v>
+        <v>0.04761904761904766</v>
       </c>
     </row>
     <row r="9">

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -762,17 +762,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Feb 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>363557.4712643678</v>
+        <v>363478.9272030651</v>
       </c>
       <c r="H9" t="n">
-        <v>-30000</v>
+        <v>-11000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1234567901234568</v>
+        <v>-0.04910714285714286</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -680,21 +680,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6.542</v>
+        <v>6.946</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dec 2025</t>
+          <t>Jan 2026</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7.796471074380164</v>
+        <v>7.769818181818183</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9660000000000002</v>
+        <v>-0.4850000000000003</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1286627597229622</v>
+        <v>-0.06526712420939312</v>
       </c>
     </row>
     <row r="8">

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>213000</v>
+        <v>205000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>363478.9272030651</v>
+        <v>363369.7318007663</v>
       </c>
       <c r="H9" t="n">
-        <v>-11000</v>
+        <v>-17000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.04910714285714286</v>
+        <v>-0.07657657657657657</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -563,21 +563,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11.256338</v>
+        <v>11.323096</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jul 2025</t>
+          <t>Oct 2025</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>11.09353892682927</v>
+        <v>11.08673258536585</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1178030000000003</v>
+        <v>0.2006219999999992</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01057616643481394</v>
+        <v>0.01803753373574972</v>
       </c>
     </row>
     <row r="5">

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205000</v>
+        <v>210000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>363369.7318007663</v>
+        <v>363266.2835249042</v>
       </c>
       <c r="H9" t="n">
-        <v>-17000</v>
+        <v>-15000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.07657657657657657</v>
+        <v>-0.06666666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -680,21 +680,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6.946</v>
+        <v>6.882</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>Feb 2026</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7.769818181818183</v>
+        <v>7.779438016528926</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4850000000000003</v>
+        <v>-0.3600000000000003</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.06526712420939312</v>
+        <v>-0.04971002485501247</v>
       </c>
     </row>
     <row r="8">

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -719,21 +719,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Feb 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4.578333333333331</v>
+        <v>4.573333333333331</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2000000000000002</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04761904761904766</v>
+        <v>0.02380952380952372</v>
       </c>
     </row>
     <row r="9">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>210000</v>
+        <v>202000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>363266.2835249042</v>
+        <v>363136.0153256705</v>
       </c>
       <c r="H9" t="n">
-        <v>-15000</v>
+        <v>-22000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.09821428571428571</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -641,21 +641,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1328986.66</v>
+        <v>1327596.44</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>Feb 2026</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1104597.812561983</v>
+        <v>1108039.984628099</v>
       </c>
       <c r="H6" t="n">
-        <v>24724.11999999988</v>
+        <v>23321.96999999997</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01895639814971599</v>
+        <v>0.01788118263175079</v>
       </c>
     </row>
     <row r="7">

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,21 +758,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>202000</v>
+        <v>219000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Apr 2026</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>363136.0153256705</v>
+        <v>363034.4827586207</v>
       </c>
       <c r="H9" t="n">
-        <v>-22000</v>
+        <v>-1000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.09821428571428571</v>
+        <v>-0.004545454545454545</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219000</v>
+        <v>207000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>363034.4827586207</v>
+        <v>362925.2873563218</v>
       </c>
       <c r="H9" t="n">
-        <v>-1000</v>
+        <v>-16000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.004545454545454545</v>
+        <v>-0.07174887892376682</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>207000</v>
+        <v>214000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>362925.2873563218</v>
+        <v>362844.8275862069</v>
       </c>
       <c r="H9" t="n">
-        <v>-16000</v>
+        <v>-3000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.07174887892376682</v>
+        <v>-0.01382488479262673</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>214000</v>
+        <v>189000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>362844.8275862069</v>
+        <v>362712.6436781609</v>
       </c>
       <c r="H9" t="n">
-        <v>-3000</v>
+        <v>-35000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.01382488479262673</v>
+        <v>-0.15625</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -680,21 +680,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6.882</v>
+        <v>6.866</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Feb 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7.779438016528926</v>
+        <v>7.788826446280993</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3600000000000003</v>
+        <v>-0.0860000000000003</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04971002485501247</v>
+        <v>-0.01237054085155355</v>
       </c>
     </row>
     <row r="8">
@@ -758,21 +758,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>189000</v>
+        <v>200000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>362712.6436781609</v>
+        <v>362565.1340996168</v>
       </c>
       <c r="H9" t="n">
-        <v>-35000</v>
+        <v>-39000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.15625</v>
+        <v>-0.1631799163179916</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -641,21 +641,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1327596.44</v>
+        <v>1336987.42</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Feb 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1108039.984628099</v>
+        <v>1111583.661322314</v>
       </c>
       <c r="H6" t="n">
-        <v>23321.96999999997</v>
+        <v>44184.86999999988</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01788118263175079</v>
+        <v>0.03417758574192159</v>
       </c>
     </row>
     <row r="7">
@@ -723,11 +723,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Apr 2026</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4.573333333333331</v>
+        <v>4.567499999999997</v>
       </c>
       <c r="H8" t="n">
         <v>0.09999999999999964</v>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>200000</v>
+        <v>211000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>362565.1340996168</v>
+        <v>362413.7931034483</v>
       </c>
       <c r="H9" t="n">
-        <v>-39000</v>
+        <v>-17000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1631799163179916</v>
+        <v>-0.07456140350877193</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -481,25 +481,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>tripwire</t>
+          <t>healthy</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Oct 2025</t>
+          <t>Jan 2026</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2.465121951219512</v>
+        <v>2.483658536585366</v>
       </c>
       <c r="H2" t="n">
         <v>-0.1400000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04545454545454549</v>
+        <v>-0.04575163398692814</v>
       </c>
     </row>
     <row r="3">
@@ -524,21 +524,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4.11</v>
+        <v>3.84</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oct 2025</t>
+          <t>Jan 2026</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3.390243902439025</v>
+        <v>3.41</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4699999999999998</v>
+        <v>-0.6200000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1026200873362445</v>
+        <v>-0.1390134529147982</v>
       </c>
     </row>
     <row r="4">
@@ -602,21 +602,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oct 2025</t>
+          <t>Jan 2026</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2.664634146341463</v>
+        <v>2.585365853658537</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005649717514124299</v>
+        <v>0.06779661016949146</v>
       </c>
     </row>
     <row r="6">

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>211000</v>
+        <v>209000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>362413.7931034483</v>
+        <v>362281.6091954023</v>
       </c>
       <c r="H9" t="n">
         <v>-17000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.07456140350877193</v>
+        <v>-0.0752212389380531</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>209000</v>
+        <v>215000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>362281.6091954023</v>
+        <v>362183.908045977</v>
       </c>
       <c r="H9" t="n">
-        <v>-17000</v>
+        <v>-10000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0752212389380531</v>
+        <v>-0.04444444444444445</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -680,21 +680,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6.866</v>
+        <v>7.618</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Apr 2026</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7.788826446280993</v>
+        <v>7.801305785123968</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0860000000000003</v>
+        <v>0.5200000000000005</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01237054085155355</v>
+        <v>0.07326007326007333</v>
       </c>
     </row>
     <row r="8">

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>215000</v>
+        <v>225000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>362183.908045977</v>
+        <v>362105.3639846743</v>
       </c>
       <c r="H9" t="n">
-        <v>-10000</v>
+        <v>-11000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.04444444444444445</v>
+        <v>-0.04661016949152542</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -723,17 +723,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4.567499999999997</v>
+        <v>4.560833333333331</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09999999999999964</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02380952380952372</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -641,21 +641,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1336987.42</v>
+        <v>1348688.3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Apr 2026</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1111583.661322314</v>
+        <v>1115116.709173554</v>
       </c>
       <c r="H6" t="n">
-        <v>44184.86999999988</v>
+        <v>49559.05000000005</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03417758574192159</v>
+        <v>0.03814789790931122</v>
       </c>
     </row>
     <row r="7">

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,21 +758,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>225000</v>
+        <v>229000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>362105.3639846743</v>
+        <v>362036.3984674329</v>
       </c>
       <c r="H9" t="n">
-        <v>-11000</v>
+        <v>-15000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.04661016949152542</v>
+        <v>-0.06147540983606557</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229000</v>
+        <v>226000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>362036.3984674329</v>
+        <v>361948.275862069</v>
       </c>
       <c r="H9" t="n">
-        <v>-15000</v>
+        <v>-20000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.06147540983606557</v>
+        <v>-0.08130081300813008</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -563,21 +563,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11.323096</v>
+        <v>11.164138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oct 2025</t>
+          <t>Jan 2026</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>11.08673258536585</v>
+        <v>11.07203170731707</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2006219999999992</v>
+        <v>0.05875699999999995</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01803753373574972</v>
+        <v>0.005290858548662126</v>
       </c>
     </row>
     <row r="5">

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>226000</v>
+        <v>215000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>361948.275862069</v>
+        <v>361862.0689655172</v>
       </c>
       <c r="H9" t="n">
-        <v>-20000</v>
+        <v>-28000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.08130081300813008</v>
+        <v>-0.1152263374485597</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -680,21 +680,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7.618</v>
+        <v>7.594</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7.801305785123968</v>
+        <v>7.815834710743803</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5200000000000005</v>
+        <v>0.2840000000000007</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07326007326007333</v>
+        <v>0.03885088919288655</v>
       </c>
     </row>
     <row r="8">

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -719,21 +719,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4.560833333333331</v>
+        <v>4.555833333333331</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.1000000000000005</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.02439024390243916</v>
       </c>
     </row>
     <row r="9">
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>361862.0689655172</v>
+        <v>361773.9463601533</v>
       </c>
       <c r="H9" t="n">
-        <v>-28000</v>
+        <v>-21000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1152263374485597</v>
+        <v>-0.08898305084745763</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -641,21 +641,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1348688.3</v>
+        <v>1344207.79</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1115116.709173554</v>
+        <v>1118587.818512397</v>
       </c>
       <c r="H6" t="n">
-        <v>49559.05000000005</v>
+        <v>44485.39000000013</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03814789790931122</v>
+        <v>0.03422683951588442</v>
       </c>
     </row>
     <row r="7">
@@ -762,17 +762,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>361773.9463601533</v>
+        <v>361701.1494252874</v>
       </c>
       <c r="H9" t="n">
-        <v>-21000</v>
+        <v>-16000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.08898305084745763</v>
+        <v>-0.06926406926406926</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>215000</v>
+        <v>208000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>361701.1494252874</v>
+        <v>361618.7739463602</v>
       </c>
       <c r="H9" t="n">
-        <v>-16000</v>
+        <v>-20000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.06926406926406926</v>
+        <v>-0.08771929824561403</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208000</v>
+        <v>187000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>361618.7739463602</v>
+        <v>361482.7586206897</v>
       </c>
       <c r="H9" t="n">
-        <v>-20000</v>
+        <v>-34000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.08771929824561403</v>
+        <v>-0.1538461538461539</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>187000</v>
+        <v>197000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>361482.7586206897</v>
+        <v>361356.3218390805</v>
       </c>
       <c r="H9" t="n">
-        <v>-34000</v>
+        <v>-21000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1538461538461539</v>
+        <v>-0.0963302752293578</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -680,21 +680,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7.594</v>
+        <v>7.359</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7.815834710743803</v>
+        <v>7.828438016528926</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2840000000000007</v>
+        <v>0.1550000000000002</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03885088919288655</v>
+        <v>0.02151582454192119</v>
       </c>
     </row>
     <row r="8">

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,21 +758,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>197000</v>
+        <v>199000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>361356.3218390805</v>
+        <v>361231.8007662835</v>
       </c>
       <c r="H9" t="n">
-        <v>-21000</v>
+        <v>-20000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0963302752293578</v>
+        <v>-0.091324200913242</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -719,21 +719,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4.555833333333331</v>
+        <v>4.549166666666665</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1000000000000005</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02439024390243916</v>
+        <v>-0.04651162790697679</v>
       </c>
     </row>
     <row r="9">

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -641,21 +641,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1344207.79</v>
+        <v>1351069.14</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1118587.818512397</v>
+        <v>1122101.756280992</v>
       </c>
       <c r="H6" t="n">
-        <v>44485.39000000013</v>
+        <v>49326.97999999998</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03422683951588442</v>
+        <v>0.03789304941924904</v>
       </c>
     </row>
     <row r="7">

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>199000</v>
+        <v>209000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>361231.8007662835</v>
+        <v>361126.4367816092</v>
       </c>
       <c r="H9" t="n">
-        <v>-20000</v>
+        <v>-17000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.091324200913242</v>
+        <v>-0.0752212389380531</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>209000</v>
+        <v>206000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>361126.4367816092</v>
+        <v>361021.0727969349</v>
       </c>
       <c r="H9" t="n">
-        <v>-17000</v>
+        <v>-18000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0752212389380531</v>
+        <v>-0.08035714285714286</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -485,21 +485,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>Apr 2026</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2.483658536585366</v>
+        <v>2.500975609756098</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1400000000000001</v>
+        <v>-0.1899999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04575163398692814</v>
+        <v>-0.06249999999999998</v>
       </c>
     </row>
     <row r="3">
@@ -524,21 +524,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>Apr 2026</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3.41</v>
+        <v>3.430731707317073</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6200000000000001</v>
+        <v>-0.3700000000000006</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1390134529147982</v>
+        <v>-0.08830548926014332</v>
       </c>
     </row>
     <row r="4">
@@ -602,21 +602,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>Apr 2026</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2.585365853658537</v>
+        <v>2.51390243902439</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1199999999999999</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06779661016949146</v>
+        <v>0.04494382022471914</v>
       </c>
     </row>
     <row r="6">

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>206000</v>
+        <v>203000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>361021.0727969349</v>
+        <v>360906.1302681993</v>
       </c>
       <c r="H9" t="n">
-        <v>-18000</v>
+        <v>-30000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.08035714285714286</v>
+        <v>-0.1287553648068669</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -680,21 +680,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7.359</v>
+        <v>7.271</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7.828438016528926</v>
+        <v>7.839611570247935</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1550000000000002</v>
+        <v>0.1819999999999995</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02151582454192119</v>
+        <v>0.02567357878403153</v>
       </c>
     </row>
     <row r="8">

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>203000</v>
+        <v>206000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>360906.1302681993</v>
+        <v>360802.6819923372</v>
       </c>
       <c r="H9" t="n">
-        <v>-30000</v>
+        <v>-23000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1287553648068669</v>
+        <v>-0.1004366812227074</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -723,11 +723,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4.549166666666665</v>
+        <v>4.543333333333332</v>
       </c>
       <c r="H8" t="n">
         <v>-0.2000000000000002</v>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -641,21 +641,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1351069.14</v>
+        <v>1357221.44</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1122101.756280992</v>
+        <v>1125650.468347108</v>
       </c>
       <c r="H6" t="n">
-        <v>49326.97999999998</v>
+        <v>46939.96999999997</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03789304941924904</v>
+        <v>0.03582434085708315</v>
       </c>
     </row>
     <row r="7">

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -762,17 +762,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aug 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>360802.6819923372</v>
+        <v>360706.8965517241</v>
       </c>
       <c r="H9" t="n">
-        <v>-23000</v>
+        <v>-30000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1004366812227074</v>
+        <v>-0.1271186440677966</v>
       </c>
     </row>
   </sheetData>
